--- a/Manual_find_invalid_versions/manual_invalid_versions_recent_installations.xlsx
+++ b/Manual_find_invalid_versions/manual_invalid_versions_recent_installations.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\falve11887\OneDrive - Elekta\Documents\Monthly Clean up automations\Manual_find_invalid_versions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elektaonlinena-my.sharepoint.com/personal/fernando_alvesdepaula_elekta_com/Documents/Documents/Monthly Clean up automations/Manual_find_invalid_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71214F1E-B106-460A-AA95-D9779CB9C09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_35093D3197652ADEE54878D6425DCE3A87450AAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EB1189B-F8FF-4E55-9DA2-411EEFFCF562}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$275</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="715">
   <si>
     <t>Warranty Start Date</t>
   </si>
@@ -2140,7 +2143,31 @@
     <t>Version in doc</t>
   </si>
   <si>
-    <t>Comment</t>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>2.2.2.003</t>
+  </si>
+  <si>
+    <t>Valid?</t>
+  </si>
+  <si>
+    <t>2.86.77</t>
+  </si>
+  <si>
+    <t>6.2.3.0</t>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
+  <si>
+    <t>2.86.84</t>
+  </si>
+  <si>
+    <t>3.2.3.2</t>
+  </si>
+  <si>
+    <t>6.2.3.1</t>
   </si>
 </sst>
 </file>
@@ -2509,17 +2536,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I275"/>
-  <sheetFormatPr defaultColWidth="17.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -8576,7 +8603,9 @@
       <c r="G251" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H251" s="3"/>
+      <c r="H251" s="3" t="s">
+        <v>710</v>
+      </c>
       <c r="I251" s="3"/>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.35">
@@ -8601,7 +8630,9 @@
       <c r="G252" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H252" s="3"/>
+      <c r="H252" s="3" t="s">
+        <v>710</v>
+      </c>
       <c r="I252" s="3"/>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.35">
@@ -8626,7 +8657,9 @@
       <c r="G253" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H253" s="3"/>
+      <c r="H253" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I253" s="3"/>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.35">
@@ -8651,7 +8684,9 @@
       <c r="G254" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H254" s="3"/>
+      <c r="H254" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I254" s="3"/>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.35">
@@ -8676,7 +8711,9 @@
       <c r="G255" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H255" s="3"/>
+      <c r="H255" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I255" s="3"/>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.35">
@@ -8701,7 +8738,9 @@
       <c r="G256" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H256" s="3"/>
+      <c r="H256" s="3" t="s">
+        <v>714</v>
+      </c>
       <c r="I256" s="3"/>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.35">
@@ -8726,7 +8765,9 @@
       <c r="G257" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H257" s="3"/>
+      <c r="H257" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I257" s="3"/>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.35">
@@ -8751,7 +8792,9 @@
       <c r="G258" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H258" s="3"/>
+      <c r="H258" s="3" t="s">
+        <v>714</v>
+      </c>
       <c r="I258" s="3"/>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.35">
@@ -8774,7 +8817,9 @@
       <c r="G259" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H259" s="3"/>
+      <c r="H259" s="3" t="s">
+        <v>380</v>
+      </c>
       <c r="I259" s="3"/>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.35">
@@ -8799,7 +8844,9 @@
       <c r="G260" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H260" s="3"/>
+      <c r="H260" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I260" s="3"/>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.35">
@@ -8824,7 +8871,9 @@
       <c r="G261" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H261" s="3"/>
+      <c r="H261" s="3" t="s">
+        <v>714</v>
+      </c>
       <c r="I261" s="3"/>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.35">
@@ -8849,7 +8898,9 @@
       <c r="G262" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H262" s="3"/>
+      <c r="H262" s="3" t="s">
+        <v>714</v>
+      </c>
       <c r="I262" s="3"/>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.35">
@@ -8874,7 +8925,9 @@
       <c r="G263" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H263" s="3"/>
+      <c r="H263" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I263" s="3"/>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.35">
@@ -8899,7 +8952,9 @@
       <c r="G264" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H264" s="3"/>
+      <c r="H264" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I264" s="3"/>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.35">
@@ -8922,7 +8977,9 @@
       <c r="G265" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H265" s="3"/>
+      <c r="H265" s="3" t="s">
+        <v>713</v>
+      </c>
       <c r="I265" s="3"/>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.35">
@@ -8947,7 +9004,9 @@
       <c r="G266" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H266" s="3"/>
+      <c r="H266" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I266" s="3"/>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.35">
@@ -8970,7 +9029,9 @@
       <c r="G267" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H267" s="3"/>
+      <c r="H267" s="3" t="s">
+        <v>712</v>
+      </c>
       <c r="I267" s="3"/>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.35">
@@ -8995,7 +9056,9 @@
       <c r="G268" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H268" s="3"/>
+      <c r="H268" s="3" t="s">
+        <v>710</v>
+      </c>
       <c r="I268" s="3"/>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.35">
@@ -9020,7 +9083,9 @@
       <c r="G269" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H269" s="3"/>
+      <c r="H269" s="3" t="s">
+        <v>710</v>
+      </c>
       <c r="I269" s="3"/>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.35">
@@ -9045,7 +9110,9 @@
       <c r="G270" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H270" s="3"/>
+      <c r="H270" s="3" t="s">
+        <v>710</v>
+      </c>
       <c r="I270" s="3"/>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.35">
@@ -9070,7 +9137,9 @@
       <c r="G271" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H271" s="3"/>
+      <c r="H271" s="3" t="s">
+        <v>710</v>
+      </c>
       <c r="I271" s="3"/>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.35">
@@ -9095,7 +9164,9 @@
       <c r="G272" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H272" s="3"/>
+      <c r="H272" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="I272" s="3"/>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.35">
@@ -9118,7 +9189,9 @@
       <c r="G273" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H273" s="3"/>
+      <c r="H273" s="3" t="s">
+        <v>707</v>
+      </c>
       <c r="I273" s="3"/>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.35">
@@ -9141,7 +9214,9 @@
       <c r="G274" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H274" s="3"/>
+      <c r="H274" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="I274" s="3"/>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.35">
@@ -9164,10 +9239,15 @@
       <c r="G275" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H275" s="3"/>
-      <c r="I275" s="3"/>
+      <c r="H275" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>708</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I275" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial"&amp;7&amp;KC8C9C8 Restricted Information and Basic Personal Data</oddFooter>
@@ -9177,6 +9257,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{8009cb06-7738-4ab2-bfa1-5e7551442bdd}" enabled="1" method="Standard" siteId="{9295d077-5563-4c2d-9456-be5c3ad9f4ec}" contentBits="2" removed="0"/>
+  <clbl:label id="{8009cb06-7738-4ab2-bfa1-5e7551442bdd}" enabled="1" method="Standard" siteId="{9295d077-5563-4c2d-9456-be5c3ad9f4ec}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/Manual_find_invalid_versions/manual_invalid_versions_recent_installations.xlsx
+++ b/Manual_find_invalid_versions/manual_invalid_versions_recent_installations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elektaonlinena-my.sharepoint.com/personal/fernando_alvesdepaula_elekta_com/Documents/Documents/Monthly Clean up automations/Manual_find_invalid_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="11_35093D3197652ADEE54878D6425DCE3A87450AAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06369809-783F-4E92-BC02-818290C20E7F}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="11_35093D3197652ADEE54878D6425DCE3A87450AAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC0F8DE-403C-45E5-9F07-11A4288F0060}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
